--- a/model/pwc_5yr.xlsx
+++ b/model/pwc_5yr.xlsx
@@ -524,19 +524,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2132955339.265</v>
+        <v>2135607762.265</v>
       </c>
       <c r="D3" t="n">
-        <v>2125056679.794275</v>
+        <v>2130442907.794275</v>
       </c>
       <c r="E3" t="n">
-        <v>2103903870.487075</v>
+        <v>2111466138.487075</v>
       </c>
       <c r="F3" t="n">
-        <v>2081370427.876622</v>
+        <v>2090842143.876622</v>
       </c>
       <c r="G3" t="n">
-        <v>2064850189.551127</v>
+        <v>2076170037.551127</v>
       </c>
     </row>
     <row r="4">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2198453865.95</v>
+        <v>2198488305.95</v>
       </c>
       <c r="D4" t="n">
-        <v>2249367546.8475</v>
+        <v>2249401986.8475</v>
       </c>
       <c r="E4" t="n">
-        <v>2288386144.139875</v>
+        <v>2288420584.139875</v>
       </c>
       <c r="F4" t="n">
-        <v>2316111254.774869</v>
+        <v>2316145694.774869</v>
       </c>
       <c r="G4" t="n">
-        <v>2348549221.661071</v>
+        <v>2348583661.661071</v>
       </c>
     </row>
     <row r="5">
@@ -605,19 +605,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2218247508.8438</v>
+        <v>2219765490.5267</v>
       </c>
       <c r="D6" t="n">
-        <v>2281101605.7124</v>
+        <v>2284184143.9968</v>
       </c>
       <c r="E6" t="n">
-        <v>2345274961.3872</v>
+        <v>2349602847.3636</v>
       </c>
       <c r="F6" t="n">
-        <v>2392564251.8034</v>
+        <v>2397984914.8702</v>
       </c>
       <c r="G6" t="n">
-        <v>2437930186.489296</v>
+        <v>2444408535.499697</v>
       </c>
     </row>
     <row r="7">
@@ -632,19 +632,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2253350895.503</v>
+        <v>2253370605.515</v>
       </c>
       <c r="D7" t="n">
-        <v>2347366106.5052</v>
+        <v>2347385816.5172</v>
       </c>
       <c r="E7" t="n">
-        <v>2443357051.3422</v>
+        <v>2443376761.3542</v>
       </c>
       <c r="F7" t="n">
-        <v>2516663654.3962</v>
+        <v>2516683364.4082</v>
       </c>
       <c r="G7" t="n">
-        <v>2587169435.335496</v>
+        <v>2587189145.347497</v>
       </c>
     </row>
     <row r="8">
@@ -686,19 +686,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-85292169.5788002</v>
+        <v>-84157728.26170015</v>
       </c>
       <c r="D9" t="n">
-        <v>-156044925.9181249</v>
+        <v>-153741236.2025249</v>
       </c>
       <c r="E9" t="n">
-        <v>-241371090.9001253</v>
+        <v>-238136708.8765256</v>
       </c>
       <c r="F9" t="n">
-        <v>-311193823.9267778</v>
+        <v>-307142770.993578</v>
       </c>
       <c r="G9" t="n">
-        <v>-373079996.938169</v>
+        <v>-368238497.9485693</v>
       </c>
     </row>
     <row r="10">
@@ -713,19 +713,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-54897029.55299997</v>
+        <v>-54882299.56500006</v>
       </c>
       <c r="D10" t="n">
-        <v>-97998559.65770006</v>
+        <v>-97983829.66970015</v>
       </c>
       <c r="E10" t="n">
-        <v>-154970907.2023253</v>
+        <v>-154956177.214325</v>
       </c>
       <c r="F10" t="n">
-        <v>-200552399.6213312</v>
+        <v>-200537669.6333313</v>
       </c>
       <c r="G10" t="n">
-        <v>-238620213.6744256</v>
+        <v>-238605483.6864257</v>
       </c>
     </row>
     <row r="11">
@@ -767,19 +767,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>987779273.1138</v>
+        <v>989297254.7967</v>
       </c>
       <c r="D12" t="n">
-        <v>979881465.5824001</v>
+        <v>982964003.8668001</v>
       </c>
       <c r="E12" t="n">
-        <v>964316265.3672</v>
+        <v>968644151.3436</v>
       </c>
       <c r="F12" t="n">
-        <v>947876372.1334001</v>
+        <v>953297035.2002001</v>
       </c>
       <c r="G12" t="n">
-        <v>934790679.6892965</v>
+        <v>941269028.6996965</v>
       </c>
     </row>
     <row r="13">
@@ -794,19 +794,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1022913859.773</v>
+        <v>1022933569.785</v>
       </c>
       <c r="D13" t="n">
-        <v>1046208366.3752</v>
+        <v>1046228076.3872</v>
       </c>
       <c r="E13" t="n">
-        <v>1062491955.3222</v>
+        <v>1062511665.3342</v>
       </c>
       <c r="F13" t="n">
-        <v>1072100574.7262</v>
+        <v>1072120284.7382</v>
       </c>
       <c r="G13" t="n">
-        <v>1084185928.535496</v>
+        <v>1084205638.547497</v>
       </c>
     </row>
     <row r="14">
@@ -821,19 +821,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9106617973718374</v>
+        <v>0.8911408953807296</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9107298367275748</v>
+        <v>0.8940451260939216</v>
       </c>
       <c r="E14" t="n">
-        <v>0.91503073988243</v>
+        <v>0.8991750964958606</v>
       </c>
       <c r="F14" t="n">
-        <v>0.904666390272873</v>
+        <v>0.8895996265611197</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8890086009459932</v>
+        <v>0.8746924449817675</v>
       </c>
     </row>
     <row r="15">
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.931345556073723</v>
+        <v>0.9122710552904771</v>
       </c>
       <c r="D15" t="n">
-        <v>0.955481884573239</v>
+        <v>0.9394826280175572</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9882836098355675</v>
+        <v>0.9732546994827147</v>
       </c>
       <c r="F15" t="n">
-        <v>1.008261714627658</v>
+        <v>0.994052532519325</v>
       </c>
       <c r="G15" t="n">
-        <v>1.022960253921377</v>
+        <v>1.009521862664477</v>
       </c>
     </row>
     <row r="16">
@@ -875,19 +875,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9328316089803083</v>
+        <v>0.9129070888009263</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9547931735666592</v>
+        <v>0.9374327313702259</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9671685341872839</v>
+        <v>0.9506028413942483</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9743406384311047</v>
+        <v>0.9583710139052983</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9755901072103361</v>
+        <v>0.9601961546302115</v>
       </c>
     </row>
     <row r="17">
@@ -902,19 +902,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.7498385218977821</v>
+        <v>0.7337650198168038</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7498945454732568</v>
+        <v>0.736156362103825</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7534359072321112</v>
+        <v>0.740380377467894</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7449019063394737</v>
+        <v>0.7324959397512089</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7320092895206521</v>
+        <v>0.7202213730203073</v>
       </c>
     </row>
     <row r="18">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.7668695196810125</v>
+        <v>0.751163584157501</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7867433619112982</v>
+        <v>0.7735695811270393</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8137522880103016</v>
+        <v>0.8013774898610432</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8302022506757534</v>
+        <v>0.8185024164011219</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8423050214407807</v>
+        <v>0.8312398560129138</v>
       </c>
     </row>
     <row r="19">
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.7680931349882008</v>
+        <v>0.7516872938691953</v>
       </c>
       <c r="D19" t="n">
-        <v>0.786176277572547</v>
+        <v>0.7718816971326583</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7963661440438341</v>
+        <v>0.7827259599118203</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8022716515117042</v>
+        <v>0.7891222697277621</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8033004635528815</v>
+        <v>0.7906250897948539</v>
       </c>
     </row>
     <row r="20">
@@ -1010,19 +1010,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.07182185495397624</v>
+        <v>0.07173265227202844</v>
       </c>
       <c r="D21" t="n">
-        <v>0.07593393415540403</v>
+        <v>0.07574195647752228</v>
       </c>
       <c r="E21" t="n">
-        <v>0.08161555212132726</v>
+        <v>0.08132324401045617</v>
       </c>
       <c r="F21" t="n">
-        <v>0.08456979528606719</v>
+        <v>0.08418668597986075</v>
       </c>
       <c r="G21" t="n">
-        <v>0.08495489788444842</v>
+        <v>0.08449170050007533</v>
       </c>
     </row>
     <row r="22">
@@ -1037,19 +1037,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.06968206673456941</v>
+        <v>0.06968097514341932</v>
       </c>
       <c r="D22" t="n">
-        <v>0.07173745981449424</v>
+        <v>0.07173636146118502</v>
       </c>
       <c r="E22" t="n">
-        <v>0.07503597084771736</v>
+        <v>0.07503484158028553</v>
       </c>
       <c r="F22" t="n">
-        <v>0.07599853877360897</v>
+        <v>0.07599740871098758</v>
       </c>
       <c r="G22" t="n">
-        <v>0.07469255290971946</v>
+        <v>0.07469145760638231</v>
       </c>
     </row>
     <row r="23">
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>49431830.4211998</v>
+        <v>50566271.73829985</v>
       </c>
       <c r="D24" t="n">
-        <v>-106613095.4969251</v>
+        <v>-103174964.4642251</v>
       </c>
       <c r="E24" t="n">
-        <v>-347984186.3970504</v>
+        <v>-341311673.3407507</v>
       </c>
       <c r="F24" t="n">
-        <v>-659178010.3238282</v>
+        <v>-648454444.3343287</v>
       </c>
       <c r="G24" t="n">
-        <v>-1032258007.261997</v>
+        <v>-1016692942.282898</v>
       </c>
     </row>
     <row r="25">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>79826970.44700003</v>
+        <v>79841700.43499994</v>
       </c>
       <c r="D25" t="n">
-        <v>-18171589.21070004</v>
+        <v>-18142129.2347002</v>
       </c>
       <c r="E25" t="n">
-        <v>-173142496.4130254</v>
+        <v>-173098306.4490252</v>
       </c>
       <c r="F25" t="n">
-        <v>-373694896.0343566</v>
+        <v>-373635976.0823565</v>
       </c>
       <c r="G25" t="n">
-        <v>-612315109.7087822</v>
+        <v>-612241459.7687821</v>
       </c>
     </row>
   </sheetData>
@@ -1261,7 +1261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1421,19 +1421,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1040319239.6</v>
+        <v>1017102690.2</v>
       </c>
       <c r="C7" t="n">
-        <v>1072636763.8</v>
+        <v>1051801175.4</v>
       </c>
       <c r="D7" t="n">
-        <v>1106189345.2</v>
+        <v>1085399069</v>
       </c>
       <c r="E7" t="n">
-        <v>1141343159.6</v>
+        <v>1120599486.2</v>
       </c>
       <c r="F7" t="n">
-        <v>1178064798.395559</v>
+        <v>1157369036.995559</v>
       </c>
     </row>
     <row r="8">
@@ -1465,19 +1465,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7498385218977821</v>
+        <v>0.7337650198168038</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7498945454732568</v>
+        <v>0.736156362103825</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7534359072321112</v>
+        <v>0.740380377467894</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7449019063394737</v>
+        <v>0.7324959397512089</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7320092895206521</v>
+        <v>0.7202213730203073</v>
       </c>
     </row>
     <row r="10">
@@ -1487,19 +1487,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9106617973718374</v>
+        <v>0.8911408953807296</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9107298367275748</v>
+        <v>0.8940451260939216</v>
       </c>
       <c r="D10" t="n">
-        <v>0.91503073988243</v>
+        <v>0.8991750964958606</v>
       </c>
       <c r="E10" t="n">
-        <v>0.904666390272873</v>
+        <v>0.8895996265611197</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8890086009459932</v>
+        <v>0.8746924449817675</v>
       </c>
     </row>
     <row r="11">
@@ -1509,172 +1509,194 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.004661797371837362</v>
+        <v>-0.01485910461927042</v>
       </c>
       <c r="C11" t="n">
-        <v>0.004729836727574765</v>
+        <v>-0.01195487390607841</v>
       </c>
       <c r="D11" t="n">
-        <v>0.009030739882429972</v>
+        <v>-0.006824903504139446</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.001333609727127039</v>
+        <v>-0.01640037343888034</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.01699139905400682</v>
+        <v>-0.03130755501823257</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>debt_service_total</t>
+          <t>required_re_rate_delta_vs_fy27_nominal</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>153192809</v>
+        <v>0.04114089538072963</v>
       </c>
       <c r="C12" t="n">
-        <v>161363914</v>
+        <v>0.04404512609392164</v>
       </c>
       <c r="D12" t="n">
-        <v>171711276</v>
+        <v>0.0491750964958606</v>
       </c>
       <c r="E12" t="n">
-        <v>176021071</v>
+        <v>0.03959962656111971</v>
       </c>
       <c r="F12" t="n">
-        <v>175419137</v>
+        <v>0.02469244498176748</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>debt_service_to_revenue_ratio</t>
+          <t>debt_service_total</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06893362116747535</v>
+        <v>153192809</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06961574587658775</v>
+        <v>161363914</v>
       </c>
       <c r="D13" t="n">
-        <v>0.07103426170275604</v>
+        <v>171711276</v>
       </c>
       <c r="E13" t="n">
-        <v>0.06981066479579355</v>
+        <v>176021071</v>
       </c>
       <c r="F13" t="n">
-        <v>0.06669465286956039</v>
+        <v>175419137</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>debt_service_headroom_vs_10pct_cap</t>
+          <t>debt_service_to_revenue_ratio</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>69039544.97399998</v>
+        <v>0.06893362116747535</v>
       </c>
       <c r="C14" t="n">
-        <v>70428350.76444003</v>
+        <v>0.06961574587658775</v>
       </c>
       <c r="D14" t="n">
-        <v>70018942.46630642</v>
+        <v>0.07103426170275604</v>
       </c>
       <c r="E14" t="n">
-        <v>76119589.04798481</v>
+        <v>0.06981066479579355</v>
       </c>
       <c r="F14" t="n">
-        <v>87599155.25062472</v>
+        <v>0.06669465286956039</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>debt_service_cap_breached</t>
+          <t>debt_service_headroom_vs_10pct_cap</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>69039544.97399998</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>70428350.76444003</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>70018942.46630642</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>76119589.04798481</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>87599155.25062472</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>unassigned_gf_balance_eoy</t>
+          <t>debt_service_cap_breached</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>91977271.89999962</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27309803.20219946</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>-66309736.66393661</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-170496439.6672888</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>-277602739.8335385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>unassigned_gf_balance_policy_floor_7_5pct</t>
+          <t>unassigned_gf_balance_eoy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>166674265.4805</v>
+        <v>91977271.89999962</v>
       </c>
       <c r="C17" t="n">
-        <v>173844198.57333</v>
+        <v>27309803.20219946</v>
       </c>
       <c r="D17" t="n">
-        <v>181297663.8497298</v>
+        <v>-66309736.66393661</v>
       </c>
       <c r="E17" t="n">
-        <v>189105495.0359886</v>
+        <v>-170496439.6672888</v>
       </c>
       <c r="F17" t="n">
-        <v>197263719.1879685</v>
+        <v>-277602739.8335385</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>unassigned_gf_balance_policy_floor_7_5pct</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>166674265.4805</v>
+      </c>
+      <c r="C18" t="n">
+        <v>173844198.57333</v>
+      </c>
+      <c r="D18" t="n">
+        <v>181297663.8497298</v>
+      </c>
+      <c r="E18" t="n">
+        <v>189105495.0359886</v>
+      </c>
+      <c r="F18" t="n">
+        <v>197263719.1879685</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>unassigned_gf_balance_floor_breached</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
         <v>1</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C19" t="n">
         <v>1</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E19" t="n">
         <v>1</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1689,7 +1711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1739,19 +1761,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2132955339.265</v>
+        <v>2135607762.265</v>
       </c>
       <c r="C2" t="n">
-        <v>2125056679.794275</v>
+        <v>2130442907.794275</v>
       </c>
       <c r="D2" t="n">
-        <v>2103903870.487075</v>
+        <v>2111466138.487075</v>
       </c>
       <c r="E2" t="n">
-        <v>2081370427.876622</v>
+        <v>2090842143.876622</v>
       </c>
       <c r="F2" t="n">
-        <v>2064850189.551127</v>
+        <v>2076170037.551127</v>
       </c>
     </row>
     <row r="3">
@@ -1761,19 +1783,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1725981606</v>
+        <v>1728634029</v>
       </c>
       <c r="C3" t="n">
-        <v>1712181488</v>
+        <v>1717567716</v>
       </c>
       <c r="D3" t="n">
-        <v>1684983864</v>
+        <v>1692546132</v>
       </c>
       <c r="E3" t="n">
-        <v>1656257858</v>
+        <v>1665729574</v>
       </c>
       <c r="F3" t="n">
-        <v>1633392765.488898</v>
+        <v>1644712613.488898</v>
       </c>
     </row>
     <row r="4">
@@ -1783,19 +1805,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>987779273.1138</v>
+        <v>989297254.7967</v>
       </c>
       <c r="C4" t="n">
-        <v>979881465.5824001</v>
+        <v>982964003.8668001</v>
       </c>
       <c r="D4" t="n">
-        <v>964316265.3672</v>
+        <v>968644151.3436</v>
       </c>
       <c r="E4" t="n">
-        <v>947876372.1334001</v>
+        <v>953297035.2002001</v>
       </c>
       <c r="F4" t="n">
-        <v>934790679.6892965</v>
+        <v>941269028.6996965</v>
       </c>
     </row>
     <row r="5">
@@ -1805,19 +1827,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2218247508.8438</v>
+        <v>2219765490.5267</v>
       </c>
       <c r="C5" t="n">
-        <v>2281101605.7124</v>
+        <v>2284184143.9968</v>
       </c>
       <c r="D5" t="n">
-        <v>2345274961.3872</v>
+        <v>2349602847.3636</v>
       </c>
       <c r="E5" t="n">
-        <v>2392564251.8034</v>
+        <v>2397984914.8702</v>
       </c>
       <c r="F5" t="n">
-        <v>2437930186.489296</v>
+        <v>2444408535.499697</v>
       </c>
     </row>
     <row r="6">
@@ -1827,19 +1849,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-85292169.5788002</v>
+        <v>-84157728.26170015</v>
       </c>
       <c r="C6" t="n">
-        <v>-156044925.9181249</v>
+        <v>-153741236.2025249</v>
       </c>
       <c r="D6" t="n">
-        <v>-241371090.9001253</v>
+        <v>-238136708.8765256</v>
       </c>
       <c r="E6" t="n">
-        <v>-311193823.9267778</v>
+        <v>-307142770.993578</v>
       </c>
       <c r="F6" t="n">
-        <v>-373079996.938169</v>
+        <v>-368238497.9485693</v>
       </c>
     </row>
     <row r="7">
@@ -1849,19 +1871,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>989442947.6</v>
+        <v>968566186.2</v>
       </c>
       <c r="C7" t="n">
-        <v>968594287.8</v>
+        <v>952066232.4</v>
       </c>
       <c r="D7" t="n">
-        <v>945141987.2</v>
+        <v>930332967</v>
       </c>
       <c r="E7" t="n">
-        <v>923514525.6</v>
+        <v>910165140.2</v>
       </c>
       <c r="F7" t="n">
-        <v>904682214.3955593</v>
+        <v>892738047.9955593</v>
       </c>
     </row>
     <row r="8">
@@ -1893,19 +1915,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7668695196810125</v>
+        <v>0.751163584157501</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7867433619112982</v>
+        <v>0.7735695811270393</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8137522880103016</v>
+        <v>0.8013774898610432</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8302022506757534</v>
+        <v>0.8185024164011219</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8423050214407807</v>
+        <v>0.8312398560129138</v>
       </c>
     </row>
     <row r="10">
@@ -1915,19 +1937,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.931345556073723</v>
+        <v>0.9122710552904771</v>
       </c>
       <c r="C10" t="n">
-        <v>0.955481884573239</v>
+        <v>0.9394826280175572</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9882836098355675</v>
+        <v>0.9732546994827147</v>
       </c>
       <c r="E10" t="n">
-        <v>1.008261714627658</v>
+        <v>0.994052532519325</v>
       </c>
       <c r="F10" t="n">
-        <v>1.022960253921377</v>
+        <v>1.009521862664477</v>
       </c>
     </row>
     <row r="11">
@@ -1937,172 +1959,194 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02534555607372302</v>
+        <v>0.006271055290477112</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04948188457323899</v>
+        <v>0.03348262801755719</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08228360983556748</v>
+        <v>0.06725469948271467</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1022617146276578</v>
+        <v>0.08805253251932499</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1169602539213771</v>
+        <v>0.1035218626644773</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>debt_service_total</t>
+          <t>required_re_rate_delta_vs_fy27_nominal</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>153192809</v>
+        <v>0.06227105529047716</v>
       </c>
       <c r="C12" t="n">
-        <v>161363914</v>
+        <v>0.08948262801755724</v>
       </c>
       <c r="D12" t="n">
-        <v>171711276</v>
+        <v>0.1232546994827147</v>
       </c>
       <c r="E12" t="n">
-        <v>176021071</v>
+        <v>0.144052532519325</v>
       </c>
       <c r="F12" t="n">
-        <v>175419137</v>
+        <v>0.1595218626644773</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>debt_service_to_revenue_ratio</t>
+          <t>debt_service_total</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07182185495397624</v>
+        <v>153192809</v>
       </c>
       <c r="C13" t="n">
-        <v>0.07593393415540403</v>
+        <v>161363914</v>
       </c>
       <c r="D13" t="n">
-        <v>0.08161555212132726</v>
+        <v>171711276</v>
       </c>
       <c r="E13" t="n">
-        <v>0.08456979528606719</v>
+        <v>176021071</v>
       </c>
       <c r="F13" t="n">
-        <v>0.08495489788444842</v>
+        <v>175419137</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>debt_service_headroom_vs_10pct_cap</t>
+          <t>debt_service_to_revenue_ratio</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>60102724.92649999</v>
+        <v>0.07173265227202844</v>
       </c>
       <c r="C14" t="n">
-        <v>51141753.97942752</v>
+        <v>0.07574195647752228</v>
       </c>
       <c r="D14" t="n">
-        <v>38679111.04870749</v>
+        <v>0.08132324401045617</v>
       </c>
       <c r="E14" t="n">
-        <v>32115971.78766224</v>
+        <v>0.08418668597986075</v>
       </c>
       <c r="F14" t="n">
-        <v>31065881.95511276</v>
+        <v>0.08449170050007533</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>debt_service_cap_breached</t>
+          <t>debt_service_headroom_vs_10pct_cap</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>60367967.2265</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>51680376.77942753</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>39435337.84870747</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>33063143.38766223</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>32197866.75511277</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>unassigned_gf_balance_eoy</t>
+          <t>debt_service_cap_breached</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>49431830.4211998</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>-106613095.4969251</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>-347984186.3970504</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-659178010.3238282</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>-1032258007.261997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>unassigned_gf_balance_policy_floor_7_5pct</t>
+          <t>unassigned_gf_balance_eoy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>159971650.444875</v>
+        <v>50566271.73829985</v>
       </c>
       <c r="C17" t="n">
-        <v>159379250.9845706</v>
+        <v>-103174964.4642251</v>
       </c>
       <c r="D17" t="n">
-        <v>157792790.2865306</v>
+        <v>-341311673.3407507</v>
       </c>
       <c r="E17" t="n">
-        <v>156102782.0907467</v>
+        <v>-648454444.3343287</v>
       </c>
       <c r="F17" t="n">
-        <v>154863764.2163346</v>
+        <v>-1016692942.282898</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>unassigned_gf_balance_policy_floor_7_5pct</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>160170582.169875</v>
+      </c>
+      <c r="C18" t="n">
+        <v>159783218.0845706</v>
+      </c>
+      <c r="D18" t="n">
+        <v>158359960.3865306</v>
+      </c>
+      <c r="E18" t="n">
+        <v>156813160.7907467</v>
+      </c>
+      <c r="F18" t="n">
+        <v>155712752.8163345</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>unassigned_gf_balance_floor_breached</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
         <v>1</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C19" t="n">
         <v>1</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E19" t="n">
         <v>1</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2117,7 +2161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2167,19 +2211,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2198453865.95</v>
+        <v>2198488305.95</v>
       </c>
       <c r="C2" t="n">
-        <v>2249367546.8475</v>
+        <v>2249401986.8475</v>
       </c>
       <c r="D2" t="n">
-        <v>2288386144.139875</v>
+        <v>2288420584.139875</v>
       </c>
       <c r="E2" t="n">
-        <v>2316111254.774869</v>
+        <v>2316145694.774869</v>
       </c>
       <c r="F2" t="n">
-        <v>2348549221.661071</v>
+        <v>2348583661.661071</v>
       </c>
     </row>
     <row r="3">
@@ -2189,19 +2233,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1787373510</v>
+        <v>1787407950</v>
       </c>
       <c r="C3" t="n">
-        <v>1828076824</v>
+        <v>1828111264</v>
       </c>
       <c r="D3" t="n">
-        <v>1856529714</v>
+        <v>1856564154</v>
       </c>
       <c r="E3" t="n">
-        <v>1873319194</v>
+        <v>1873353634</v>
       </c>
       <c r="F3" t="n">
-        <v>1894436359.488898</v>
+        <v>1894470799.488898</v>
       </c>
     </row>
     <row r="4">
@@ -2211,19 +2255,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1022913859.773</v>
+        <v>1022933569.785</v>
       </c>
       <c r="C4" t="n">
-        <v>1046208366.3752</v>
+        <v>1046228076.3872</v>
       </c>
       <c r="D4" t="n">
-        <v>1062491955.3222</v>
+        <v>1062511665.3342</v>
       </c>
       <c r="E4" t="n">
-        <v>1072100574.7262</v>
+        <v>1072120284.7382</v>
       </c>
       <c r="F4" t="n">
-        <v>1084185928.535496</v>
+        <v>1084205638.547497</v>
       </c>
     </row>
     <row r="5">
@@ -2233,19 +2277,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2253350895.503</v>
+        <v>2253370605.515</v>
       </c>
       <c r="C5" t="n">
-        <v>2347366106.5052</v>
+        <v>2347385816.5172</v>
       </c>
       <c r="D5" t="n">
-        <v>2443357051.3422</v>
+        <v>2443376761.3542</v>
       </c>
       <c r="E5" t="n">
-        <v>2516663654.3962</v>
+        <v>2516683364.4082</v>
       </c>
       <c r="F5" t="n">
-        <v>2587169435.335496</v>
+        <v>2587189145.347497</v>
       </c>
     </row>
     <row r="6">
@@ -2255,19 +2299,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-54897029.55299997</v>
+        <v>-54882299.56500006</v>
       </c>
       <c r="C6" t="n">
-        <v>-97998559.65770006</v>
+        <v>-97983829.66970015</v>
       </c>
       <c r="D6" t="n">
-        <v>-154970907.2023253</v>
+        <v>-154956177.214325</v>
       </c>
       <c r="E6" t="n">
-        <v>-200552399.6213312</v>
+        <v>-200537669.6333313</v>
       </c>
       <c r="F6" t="n">
-        <v>-238620213.6744256</v>
+        <v>-238605483.6864257</v>
       </c>
     </row>
     <row r="7">
@@ -2277,19 +2321,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1032106363.6</v>
+        <v>1008903590.2</v>
       </c>
       <c r="C7" t="n">
-        <v>1047973887.8</v>
+        <v>1027152075.4</v>
       </c>
       <c r="D7" t="n">
-        <v>1058900669.2</v>
+        <v>1038124169</v>
       </c>
       <c r="E7" t="n">
-        <v>1065121283.6</v>
+        <v>1044391386.2</v>
       </c>
       <c r="F7" t="n">
-        <v>1073031922.395559</v>
+        <v>1052349936.995559</v>
       </c>
     </row>
     <row r="8">
@@ -2321,19 +2365,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7680931349882008</v>
+        <v>0.7516872938691953</v>
       </c>
       <c r="C9" t="n">
-        <v>0.786176277572547</v>
+        <v>0.7718816971326583</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7963661440438341</v>
+        <v>0.7827259599118203</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8022716515117042</v>
+        <v>0.7891222697277621</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8033004635528815</v>
+        <v>0.7906250897948539</v>
       </c>
     </row>
     <row r="10">
@@ -2343,19 +2387,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9328316089803083</v>
+        <v>0.9129070888009263</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9547931735666592</v>
+        <v>0.9374327313702259</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9671685341872839</v>
+        <v>0.9506028413942483</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9743406384311047</v>
+        <v>0.9583710139052983</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9755901072103361</v>
+        <v>0.9601961546302115</v>
       </c>
     </row>
     <row r="11">
@@ -2365,172 +2409,194 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02683160898030823</v>
+        <v>0.006907088800926275</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04879317356665913</v>
+        <v>0.03143273137022584</v>
       </c>
       <c r="D11" t="n">
-        <v>0.06116853418728385</v>
+        <v>0.0446028413942483</v>
       </c>
       <c r="E11" t="n">
-        <v>0.06834063843110472</v>
+        <v>0.0523710139052983</v>
       </c>
       <c r="F11" t="n">
-        <v>0.06959010721033609</v>
+        <v>0.05419615463021143</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>debt_service_total</t>
+          <t>required_re_rate_delta_vs_fy27_nominal</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>153192809</v>
+        <v>0.06290708880092633</v>
       </c>
       <c r="C12" t="n">
-        <v>161363914</v>
+        <v>0.08743273137022589</v>
       </c>
       <c r="D12" t="n">
-        <v>171711276</v>
+        <v>0.1006028413942484</v>
       </c>
       <c r="E12" t="n">
-        <v>176021071</v>
+        <v>0.1083710139052984</v>
       </c>
       <c r="F12" t="n">
-        <v>175419137</v>
+        <v>0.1101961546302115</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>debt_service_to_revenue_ratio</t>
+          <t>debt_service_total</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06968206673456941</v>
+        <v>153192809</v>
       </c>
       <c r="C13" t="n">
-        <v>0.07173745981449424</v>
+        <v>161363914</v>
       </c>
       <c r="D13" t="n">
-        <v>0.07503597084771736</v>
+        <v>171711276</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07599853877360897</v>
+        <v>176021071</v>
       </c>
       <c r="F13" t="n">
-        <v>0.07469255290971946</v>
+        <v>175419137</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>debt_service_headroom_vs_10pct_cap</t>
+          <t>debt_service_to_revenue_ratio</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>66652577.595</v>
+        <v>0.06968097514341932</v>
       </c>
       <c r="C14" t="n">
-        <v>63572840.68474999</v>
+        <v>0.07173636146118502</v>
       </c>
       <c r="D14" t="n">
-        <v>57127338.41398752</v>
+        <v>0.07503484158028553</v>
       </c>
       <c r="E14" t="n">
-        <v>55590054.47748691</v>
+        <v>0.07599740871098758</v>
       </c>
       <c r="F14" t="n">
-        <v>59435785.16610709</v>
+        <v>0.07469145760638231</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>debt_service_cap_breached</t>
+          <t>debt_service_headroom_vs_10pct_cap</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>66656021.595</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>63576284.68474999</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>57130782.41398752</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>55593498.47748691</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>59439229.16610709</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>unassigned_gf_balance_eoy</t>
+          <t>debt_service_cap_breached</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>79826970.44700003</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>-18171589.21070004</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>-173142496.4130254</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-373694896.0343566</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>-612315109.7087822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>unassigned_gf_balance_policy_floor_7_5pct</t>
+          <t>unassigned_gf_balance_eoy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>164884039.94625</v>
+        <v>79841700.43499994</v>
       </c>
       <c r="C17" t="n">
-        <v>168702566.0135625</v>
+        <v>-18142129.2347002</v>
       </c>
       <c r="D17" t="n">
-        <v>171628960.8104906</v>
+        <v>-173098306.4490252</v>
       </c>
       <c r="E17" t="n">
-        <v>173708344.1081152</v>
+        <v>-373635976.0823565</v>
       </c>
       <c r="F17" t="n">
-        <v>176141191.6245803</v>
+        <v>-612241459.7687821</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>unassigned_gf_balance_policy_floor_7_5pct</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>164886622.94625</v>
+      </c>
+      <c r="C18" t="n">
+        <v>168705149.0135625</v>
+      </c>
+      <c r="D18" t="n">
+        <v>171631543.8104906</v>
+      </c>
+      <c r="E18" t="n">
+        <v>173710927.1081152</v>
+      </c>
+      <c r="F18" t="n">
+        <v>176143774.6245803</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>unassigned_gf_balance_floor_breached</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
         <v>1</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C19" t="n">
         <v>1</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E19" t="n">
         <v>1</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2731,19 +2797,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>437439174</v>
+        <v>485962428</v>
       </c>
       <c r="D7" t="n">
-        <v>475019412</v>
+        <v>529624166</v>
       </c>
       <c r="E7" t="n">
-        <v>493836788</v>
+        <v>548683640</v>
       </c>
       <c r="F7" t="n">
-        <v>506321719</v>
+        <v>561413618</v>
       </c>
       <c r="G7" t="n">
-        <v>523200663.4888983</v>
+        <v>578540607.4888983</v>
       </c>
     </row>
     <row r="8">
@@ -2812,19 +2878,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>33508608</v>
+        <v>27923840</v>
       </c>
       <c r="D10" t="n">
-        <v>32545705</v>
+        <v>21697136</v>
       </c>
       <c r="E10" t="n">
-        <v>31610471</v>
+        <v>21073648</v>
       </c>
       <c r="F10" t="n">
-        <v>30702113</v>
+        <v>20468075</v>
       </c>
       <c r="G10" t="n">
-        <v>29819857</v>
+        <v>19879905</v>
       </c>
     </row>
     <row r="11">
@@ -2947,19 +3013,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>162469837</v>
+        <v>162483837</v>
       </c>
       <c r="D15" t="n">
-        <v>157369242</v>
+        <v>157396822</v>
       </c>
       <c r="E15" t="n">
-        <v>152421665</v>
+        <v>152462418</v>
       </c>
       <c r="F15" t="n">
-        <v>147622515</v>
+        <v>147676045</v>
       </c>
       <c r="G15" t="n">
-        <v>142967340</v>
+        <v>143033264</v>
       </c>
     </row>
     <row r="16">
@@ -3055,19 +3121,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>651997441</v>
+        <v>611697378</v>
       </c>
       <c r="D19" t="n">
-        <v>621217281</v>
+        <v>582819744</v>
       </c>
       <c r="E19" t="n">
-        <v>595185607</v>
+        <v>558397093</v>
       </c>
       <c r="F19" t="n">
-        <v>573363323</v>
+        <v>537923648</v>
       </c>
       <c r="G19" t="n">
-        <v>552434609</v>
+        <v>518288541</v>
       </c>
     </row>
     <row r="20">
@@ -3271,19 +3337,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>438367824</v>
+        <v>486833678</v>
       </c>
       <c r="D27" t="n">
-        <v>475948062</v>
+        <v>530495416</v>
       </c>
       <c r="E27" t="n">
-        <v>501180938</v>
+        <v>555970390</v>
       </c>
       <c r="F27" t="n">
-        <v>514652869</v>
+        <v>569687368</v>
       </c>
       <c r="G27" t="n">
-        <v>532354313.4888983</v>
+        <v>587636857.4888983</v>
       </c>
     </row>
     <row r="28">
@@ -3352,19 +3418,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>35053794</v>
+        <v>29211495</v>
       </c>
       <c r="D30" t="n">
-        <v>35616478</v>
+        <v>23744318</v>
       </c>
       <c r="E30" t="n">
-        <v>36188193</v>
+        <v>24125462</v>
       </c>
       <c r="F30" t="n">
-        <v>36769086</v>
+        <v>24512724</v>
       </c>
       <c r="G30" t="n">
-        <v>37359303</v>
+        <v>24906202</v>
       </c>
     </row>
     <row r="31">
@@ -3487,19 +3553,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>168181183</v>
+        <v>168153183</v>
       </c>
       <c r="D35" t="n">
-        <v>168634183</v>
+        <v>168578183</v>
       </c>
       <c r="E35" t="n">
-        <v>169087183</v>
+        <v>169003183</v>
       </c>
       <c r="F35" t="n">
-        <v>169540183</v>
+        <v>169428183</v>
       </c>
       <c r="G35" t="n">
-        <v>169993183</v>
+        <v>169853183</v>
       </c>
     </row>
     <row r="36">
@@ -3595,19 +3661,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>688578051</v>
+        <v>646016936</v>
       </c>
       <c r="D39" t="n">
-        <v>688960480</v>
+        <v>646375726</v>
       </c>
       <c r="E39" t="n">
-        <v>689341111</v>
+        <v>646732830</v>
       </c>
       <c r="F39" t="n">
-        <v>689719953</v>
+        <v>647088256</v>
       </c>
       <c r="G39" t="n">
-        <v>690097014</v>
+        <v>647442011</v>
       </c>
     </row>
     <row r="40">
@@ -3811,19 +3877,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>458900014</v>
+        <v>507331428</v>
       </c>
       <c r="D47" t="n">
-        <v>537605252</v>
+        <v>592118166</v>
       </c>
       <c r="E47" t="n">
-        <v>619402628</v>
+        <v>674157640</v>
       </c>
       <c r="F47" t="n">
-        <v>705207559</v>
+        <v>760207618</v>
       </c>
       <c r="G47" t="n">
-        <v>794936503.4888983</v>
+        <v>850184607.4888983</v>
       </c>
     </row>
     <row r="48">
@@ -3892,19 +3958,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>35053794</v>
+        <v>29211495</v>
       </c>
       <c r="D50" t="n">
-        <v>35616478</v>
+        <v>23744318</v>
       </c>
       <c r="E50" t="n">
-        <v>36188193</v>
+        <v>24125462</v>
       </c>
       <c r="F50" t="n">
-        <v>36769086</v>
+        <v>24512724</v>
       </c>
       <c r="G50" t="n">
-        <v>37359303</v>
+        <v>24906202</v>
       </c>
     </row>
     <row r="51">
@@ -4027,19 +4093,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>168181183</v>
+        <v>168153183</v>
       </c>
       <c r="D55" t="n">
-        <v>168634183</v>
+        <v>168578183</v>
       </c>
       <c r="E55" t="n">
-        <v>169087183</v>
+        <v>169003183</v>
       </c>
       <c r="F55" t="n">
-        <v>169540183</v>
+        <v>169428183</v>
       </c>
       <c r="G55" t="n">
-        <v>169993183</v>
+        <v>169853183</v>
       </c>
     </row>
     <row r="56">
@@ -4135,19 +4201,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>688578051</v>
+        <v>646016936</v>
       </c>
       <c r="D59" t="n">
-        <v>688960480</v>
+        <v>646375726</v>
       </c>
       <c r="E59" t="n">
-        <v>689341111</v>
+        <v>646732830</v>
       </c>
       <c r="F59" t="n">
-        <v>689719953</v>
+        <v>647088256</v>
       </c>
       <c r="G59" t="n">
-        <v>690097014</v>
+        <v>647442011</v>
       </c>
     </row>
     <row r="60">
@@ -4725,19 +4791,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>987779273.1138</v>
+        <v>989297254.7967</v>
       </c>
       <c r="E16" t="n">
-        <v>979881465.5824001</v>
+        <v>982964003.8668001</v>
       </c>
       <c r="F16" t="n">
-        <v>964316265.3672</v>
+        <v>968644151.3436</v>
       </c>
       <c r="G16" t="n">
-        <v>947876372.1334001</v>
+        <v>953297035.2002001</v>
       </c>
       <c r="H16" t="n">
-        <v>934790679.6892965</v>
+        <v>941269028.6996965</v>
       </c>
     </row>
     <row r="17">
@@ -5205,19 +5271,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1022913859.773</v>
+        <v>1022933569.785</v>
       </c>
       <c r="E31" t="n">
-        <v>1046208366.3752</v>
+        <v>1046228076.3872</v>
       </c>
       <c r="F31" t="n">
-        <v>1062491955.3222</v>
+        <v>1062511665.3342</v>
       </c>
       <c r="G31" t="n">
-        <v>1072100574.7262</v>
+        <v>1072120284.7382</v>
       </c>
       <c r="H31" t="n">
-        <v>1084185928.535496</v>
+        <v>1084205638.547497</v>
       </c>
     </row>
     <row r="32">
@@ -5773,19 +5839,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60102724.92649999</v>
+        <v>60367967.2265</v>
       </c>
       <c r="C3" t="n">
-        <v>50918877.97942752</v>
+        <v>51471276.77942753</v>
       </c>
       <c r="D3" t="n">
-        <v>38456235.04870749</v>
+        <v>39226237.84870747</v>
       </c>
       <c r="E3" t="n">
-        <v>31893095.78766224</v>
+        <v>32854043.38766223</v>
       </c>
       <c r="F3" t="n">
-        <v>30843005.95511276</v>
+        <v>31988766.75511277</v>
       </c>
     </row>
     <row r="4">
@@ -5795,19 +5861,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07182185495397624</v>
+        <v>0.07173265227202844</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07601365729900419</v>
+        <v>0.07581636918644251</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08170210283367965</v>
+        <v>0.08140385883335952</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08466045085795723</v>
+        <v>0.0842709633055249</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08504669566929454</v>
+        <v>0.08457688150935559</v>
       </c>
     </row>
     <row r="5">
@@ -5839,19 +5905,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>987779273.1138</v>
+        <v>989297254.7967</v>
       </c>
       <c r="C6" t="n">
-        <v>978605946.2344</v>
+        <v>981767324.5668</v>
       </c>
       <c r="D6" t="n">
-        <v>963040746.0192001</v>
+        <v>967447472.0436001</v>
       </c>
       <c r="E6" t="n">
-        <v>946600852.7854</v>
+        <v>952100355.9002</v>
       </c>
       <c r="F6" t="n">
-        <v>933515160.3412966</v>
+        <v>940072349.3996966</v>
       </c>
     </row>
     <row r="7">
@@ -5861,19 +5927,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1725981606</v>
+        <v>1728634029</v>
       </c>
       <c r="C7" t="n">
-        <v>1709952728</v>
+        <v>1715476716</v>
       </c>
       <c r="D7" t="n">
-        <v>1682755104</v>
+        <v>1690455132</v>
       </c>
       <c r="E7" t="n">
-        <v>1654029098</v>
+        <v>1663638574</v>
       </c>
       <c r="F7" t="n">
-        <v>1631164005.488898</v>
+        <v>1642621613.488898</v>
       </c>
     </row>
     <row r="8">
@@ -5883,19 +5949,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-85292169.5788002</v>
+        <v>-84157728.26170015</v>
       </c>
       <c r="C8" t="n">
-        <v>-156998166.5701249</v>
+        <v>-154635556.9025247</v>
       </c>
       <c r="D8" t="n">
-        <v>-242324331.5521252</v>
+        <v>-239031029.5765259</v>
       </c>
       <c r="E8" t="n">
-        <v>-312147064.5787778</v>
+        <v>-308037091.6935778</v>
       </c>
       <c r="F8" t="n">
-        <v>-374033237.590169</v>
+        <v>-369132818.6485691</v>
       </c>
     </row>
     <row r="9">
@@ -5905,19 +5971,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2218247508.8438</v>
+        <v>2219765490.5267</v>
       </c>
       <c r="C9" t="n">
-        <v>2279826086.3644</v>
+        <v>2282987464.6968</v>
       </c>
       <c r="D9" t="n">
-        <v>2343999442.0392</v>
+        <v>2348406168.063601</v>
       </c>
       <c r="E9" t="n">
-        <v>2391288732.4554</v>
+        <v>2396788235.5702</v>
       </c>
       <c r="F9" t="n">
-        <v>2436654667.141296</v>
+        <v>2443211856.199697</v>
       </c>
     </row>
     <row r="10">
@@ -5927,19 +5993,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2132955339.265</v>
+        <v>2135607762.265</v>
       </c>
       <c r="C10" t="n">
-        <v>2122827919.794275</v>
+        <v>2128351907.794275</v>
       </c>
       <c r="D10" t="n">
-        <v>2101675110.487075</v>
+        <v>2109375138.487075</v>
       </c>
       <c r="E10" t="n">
-        <v>2079141667.876622</v>
+        <v>2088751143.876622</v>
       </c>
       <c r="F10" t="n">
-        <v>2062621429.551127</v>
+        <v>2074079037.551127</v>
       </c>
     </row>
     <row r="11">
@@ -5949,19 +6015,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49431830.4211998</v>
+        <v>50566271.73829985</v>
       </c>
       <c r="C11" t="n">
-        <v>-107566336.1489251</v>
+        <v>-104069285.1642249</v>
       </c>
       <c r="D11" t="n">
-        <v>-349890667.7010503</v>
+        <v>-343100314.7407508</v>
       </c>
       <c r="E11" t="n">
-        <v>-662037732.2798281</v>
+        <v>-651137406.4343286</v>
       </c>
       <c r="F11" t="n">
-        <v>-1036070969.869997</v>
+        <v>-1020270225.082898</v>
       </c>
     </row>
     <row r="12">
@@ -5993,19 +6059,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>159971650.444875</v>
+        <v>160170582.169875</v>
       </c>
       <c r="C13" t="n">
-        <v>159212093.9845706</v>
+        <v>159626393.0845706</v>
       </c>
       <c r="D13" t="n">
-        <v>157625633.2865306</v>
+        <v>158203135.3865306</v>
       </c>
       <c r="E13" t="n">
-        <v>155935625.0907467</v>
+        <v>156656335.7907467</v>
       </c>
       <c r="F13" t="n">
-        <v>154696607.2163346</v>
+        <v>155555927.8163345</v>
       </c>
     </row>
   </sheetData>
@@ -12911,12 +12977,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>PWC-REV-FY26-30</t>
+          <t>FY27-ADOPTED</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Meals rate: 4% through 2025-12-31; 3% from 2026-01-01. FY26 is half-half, FY27+ is 3% full-year. Effective FY27 rate is 3%.</t>
+          <t>Meals-rate schedule: 4% through 2025-12-31; 3% from 2026-01-01 (FY26 blended 3.5%); 2% from 2027-01-01 per FY27 adopted (Adoption memo p.2). FY27 is 3% H1 + 2% H2 = blended 2.5%; FY28+ are full 2%. Year-specific rates encoded in model.revenue_drivers.MEALS_RATE_BY_FY.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -12935,7 +13001,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="M126" t="n">
         <v/>

--- a/model/pwc_5yr.xlsx
+++ b/model/pwc_5yr.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pre-Cancel DG" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAPEX Spillover" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partial Recovery" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="revenue_detail" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="expenditure_detail" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="impairment_sensitivity" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="validation_pre_cancellation_dg" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Pre-Cancel DG" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CAPEX Spillover" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Partial Recovery" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="revenue_detail" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="expenditure_detail" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="impairment_sensitivity" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="validation_pre_cancellation_dg" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="assumptions" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -524,19 +524,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2135607762.265</v>
+        <v>2135583162.265</v>
       </c>
       <c r="D3" t="n">
-        <v>2130442907.794275</v>
+        <v>2130418307.794275</v>
       </c>
       <c r="E3" t="n">
-        <v>2111466138.487075</v>
+        <v>2111441538.487075</v>
       </c>
       <c r="F3" t="n">
-        <v>2090842143.876622</v>
+        <v>2090817543.876622</v>
       </c>
       <c r="G3" t="n">
-        <v>2076170037.551127</v>
+        <v>2076145437.551127</v>
       </c>
     </row>
     <row r="4">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2198488305.95</v>
+        <v>2198479080.95</v>
       </c>
       <c r="D4" t="n">
-        <v>2249401986.8475</v>
+        <v>2249392761.8475</v>
       </c>
       <c r="E4" t="n">
-        <v>2288420584.139875</v>
+        <v>2288411359.139875</v>
       </c>
       <c r="F4" t="n">
-        <v>2316145694.774869</v>
+        <v>2316136469.774869</v>
       </c>
       <c r="G4" t="n">
-        <v>2348583661.661071</v>
+        <v>2348574436.661071</v>
       </c>
     </row>
     <row r="5">
@@ -605,19 +605,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2219765490.5267</v>
+        <v>2219751411.9467</v>
       </c>
       <c r="D6" t="n">
-        <v>2284184143.9968</v>
+        <v>2284170065.4168</v>
       </c>
       <c r="E6" t="n">
-        <v>2349602847.3636</v>
+        <v>2349588768.7836</v>
       </c>
       <c r="F6" t="n">
-        <v>2397984914.8702</v>
+        <v>2397970836.2902</v>
       </c>
       <c r="G6" t="n">
-        <v>2444408535.499697</v>
+        <v>2444394456.919696</v>
       </c>
     </row>
     <row r="7">
@@ -632,19 +632,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2253370605.515</v>
+        <v>2253365326.0475</v>
       </c>
       <c r="D7" t="n">
-        <v>2347385816.5172</v>
+        <v>2347380537.0497</v>
       </c>
       <c r="E7" t="n">
-        <v>2443376761.3542</v>
+        <v>2443371481.8867</v>
       </c>
       <c r="F7" t="n">
-        <v>2516683364.4082</v>
+        <v>2516678084.9407</v>
       </c>
       <c r="G7" t="n">
-        <v>2587189145.347497</v>
+        <v>2587183865.879996</v>
       </c>
     </row>
     <row r="8">
@@ -686,19 +686,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-84157728.26170015</v>
+        <v>-84168249.68170023</v>
       </c>
       <c r="D9" t="n">
-        <v>-153741236.2025249</v>
+        <v>-153751757.622525</v>
       </c>
       <c r="E9" t="n">
-        <v>-238136708.8765256</v>
+        <v>-238147230.2965257</v>
       </c>
       <c r="F9" t="n">
-        <v>-307142770.993578</v>
+        <v>-307153292.413578</v>
       </c>
       <c r="G9" t="n">
-        <v>-368238497.9485693</v>
+        <v>-368249019.3685689</v>
       </c>
     </row>
     <row r="10">
@@ -713,19 +713,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-54882299.56500006</v>
+        <v>-54886245.09750032</v>
       </c>
       <c r="D10" t="n">
-        <v>-97983829.66970015</v>
+        <v>-97987775.20219994</v>
       </c>
       <c r="E10" t="n">
-        <v>-154956177.214325</v>
+        <v>-154960122.7468252</v>
       </c>
       <c r="F10" t="n">
-        <v>-200537669.6333313</v>
+        <v>-200541615.1658311</v>
       </c>
       <c r="G10" t="n">
-        <v>-238605483.6864257</v>
+        <v>-238609429.2189255</v>
       </c>
     </row>
     <row r="11">
@@ -767,19 +767,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>989297254.7967</v>
+        <v>989283176.2167001</v>
       </c>
       <c r="D12" t="n">
-        <v>982964003.8668001</v>
+        <v>982949925.2868</v>
       </c>
       <c r="E12" t="n">
-        <v>968644151.3436</v>
+        <v>968630072.7636001</v>
       </c>
       <c r="F12" t="n">
-        <v>953297035.2002001</v>
+        <v>953282956.6202</v>
       </c>
       <c r="G12" t="n">
-        <v>941269028.6996965</v>
+        <v>941254950.1196965</v>
       </c>
     </row>
     <row r="13">
@@ -794,19 +794,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1022933569.785</v>
+        <v>1022928290.3175</v>
       </c>
       <c r="D13" t="n">
-        <v>1046228076.3872</v>
+        <v>1046222796.9197</v>
       </c>
       <c r="E13" t="n">
-        <v>1062511665.3342</v>
+        <v>1062506385.8667</v>
       </c>
       <c r="F13" t="n">
-        <v>1072120284.7382</v>
+        <v>1072115005.2707</v>
       </c>
       <c r="G13" t="n">
-        <v>1084205638.547497</v>
+        <v>1084200359.079997</v>
       </c>
     </row>
     <row r="14">
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9122710552904771</v>
+        <v>0.9122716457964342</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9394826280175572</v>
+        <v>0.9394832069449661</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9732546994827147</v>
+        <v>0.9732552670586057</v>
       </c>
       <c r="F15" t="n">
-        <v>0.994052532519325</v>
+        <v>0.9940530889662771</v>
       </c>
       <c r="G15" t="n">
-        <v>1.009521862664477</v>
+        <v>1.009522408200704</v>
       </c>
     </row>
     <row r="16">
@@ -875,19 +875,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9129070888009263</v>
+        <v>0.91290730809076</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9374327313702259</v>
+        <v>0.9374329442729767</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9506028413942483</v>
+        <v>0.9506030449932109</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9583710139052983</v>
+        <v>0.9583712106192714</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9601961546302115</v>
+        <v>0.9601963446920212</v>
       </c>
     </row>
     <row r="17">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.751163584157501</v>
+        <v>0.7511640703798452</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7735695811270393</v>
+        <v>0.7735700578156122</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8013774898610432</v>
+        <v>0.8013779572027812</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8185024164011219</v>
+        <v>0.8185028745792965</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8312398560129138</v>
+        <v>0.8312403052072024</v>
       </c>
     </row>
     <row r="19">
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.7516872938691953</v>
+        <v>0.7516874744323476</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7718816971326583</v>
+        <v>0.7718818724366894</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7827259599118203</v>
+        <v>0.7827261275551162</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7891222697277621</v>
+        <v>0.7891224317019607</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7906250897948539</v>
+        <v>0.7906252462916642</v>
       </c>
     </row>
     <row r="20">
@@ -1010,19 +1010,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.07173265227202844</v>
+        <v>0.07173347856775743</v>
       </c>
       <c r="D21" t="n">
-        <v>0.07574195647752228</v>
+        <v>0.07574283107201978</v>
       </c>
       <c r="E21" t="n">
-        <v>0.08132324401045617</v>
+        <v>0.0813241914919593</v>
       </c>
       <c r="F21" t="n">
-        <v>0.08418668597986075</v>
+        <v>0.08418767649789095</v>
       </c>
       <c r="G21" t="n">
-        <v>0.08449170050007533</v>
+        <v>0.08449270163217075</v>
       </c>
     </row>
     <row r="22">
@@ -1037,19 +1037,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.06968097514341932</v>
+        <v>0.06968126753055244</v>
       </c>
       <c r="D22" t="n">
-        <v>0.07173636146118502</v>
+        <v>0.07173665565966636</v>
       </c>
       <c r="E22" t="n">
-        <v>0.07503484158028553</v>
+        <v>0.07503514405930042</v>
       </c>
       <c r="F22" t="n">
-        <v>0.07599740871098758</v>
+        <v>0.07599771140303725</v>
       </c>
       <c r="G22" t="n">
-        <v>0.07469145760638231</v>
+        <v>0.07469175098805489</v>
       </c>
     </row>
     <row r="23">
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>50566271.73829985</v>
+        <v>50555750.31829977</v>
       </c>
       <c r="D24" t="n">
-        <v>-103174964.4642251</v>
+        <v>-103196007.3042252</v>
       </c>
       <c r="E24" t="n">
-        <v>-341311673.3407507</v>
+        <v>-341343237.6007509</v>
       </c>
       <c r="F24" t="n">
-        <v>-648454444.3343287</v>
+        <v>-648496530.014329</v>
       </c>
       <c r="G24" t="n">
-        <v>-1016692942.282898</v>
+        <v>-1016745549.382898</v>
       </c>
     </row>
     <row r="25">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>79841700.43499994</v>
+        <v>79837754.90249968</v>
       </c>
       <c r="D25" t="n">
-        <v>-18142129.2347002</v>
+        <v>-18150020.29970026</v>
       </c>
       <c r="E25" t="n">
-        <v>-173098306.4490252</v>
+        <v>-173110143.0465255</v>
       </c>
       <c r="F25" t="n">
-        <v>-373635976.0823565</v>
+        <v>-373651758.2123566</v>
       </c>
       <c r="G25" t="n">
-        <v>-612241459.7687821</v>
+        <v>-612261187.431282</v>
       </c>
     </row>
   </sheetData>
@@ -1531,19 +1531,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04114089538072963</v>
+        <v>0.02614089538072961</v>
       </c>
       <c r="C12" t="n">
-        <v>0.04404512609392164</v>
+        <v>0.02904512609392162</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0491750964958606</v>
+        <v>0.03417509649586059</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03959962656111971</v>
+        <v>0.02459962656111969</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02469244498176748</v>
+        <v>0.009692444981767467</v>
       </c>
     </row>
     <row r="13">
@@ -1761,19 +1761,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2135607762.265</v>
+        <v>2135583162.265</v>
       </c>
       <c r="C2" t="n">
-        <v>2130442907.794275</v>
+        <v>2130418307.794275</v>
       </c>
       <c r="D2" t="n">
-        <v>2111466138.487075</v>
+        <v>2111441538.487075</v>
       </c>
       <c r="E2" t="n">
-        <v>2090842143.876622</v>
+        <v>2090817543.876622</v>
       </c>
       <c r="F2" t="n">
-        <v>2076170037.551127</v>
+        <v>2076145437.551127</v>
       </c>
     </row>
     <row r="3">
@@ -1783,19 +1783,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1728634029</v>
+        <v>1728609429</v>
       </c>
       <c r="C3" t="n">
-        <v>1717567716</v>
+        <v>1717543116</v>
       </c>
       <c r="D3" t="n">
-        <v>1692546132</v>
+        <v>1692521532</v>
       </c>
       <c r="E3" t="n">
-        <v>1665729574</v>
+        <v>1665704974</v>
       </c>
       <c r="F3" t="n">
-        <v>1644712613.488898</v>
+        <v>1644688013.488898</v>
       </c>
     </row>
     <row r="4">
@@ -1805,19 +1805,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>989297254.7967</v>
+        <v>989283176.2167001</v>
       </c>
       <c r="C4" t="n">
-        <v>982964003.8668001</v>
+        <v>982949925.2868</v>
       </c>
       <c r="D4" t="n">
-        <v>968644151.3436</v>
+        <v>968630072.7636001</v>
       </c>
       <c r="E4" t="n">
-        <v>953297035.2002001</v>
+        <v>953282956.6202</v>
       </c>
       <c r="F4" t="n">
-        <v>941269028.6996965</v>
+        <v>941254950.1196965</v>
       </c>
     </row>
     <row r="5">
@@ -1827,19 +1827,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2219765490.5267</v>
+        <v>2219751411.9467</v>
       </c>
       <c r="C5" t="n">
-        <v>2284184143.9968</v>
+        <v>2284170065.4168</v>
       </c>
       <c r="D5" t="n">
-        <v>2349602847.3636</v>
+        <v>2349588768.7836</v>
       </c>
       <c r="E5" t="n">
-        <v>2397984914.8702</v>
+        <v>2397970836.2902</v>
       </c>
       <c r="F5" t="n">
-        <v>2444408535.499697</v>
+        <v>2444394456.919696</v>
       </c>
     </row>
     <row r="6">
@@ -1849,19 +1849,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-84157728.26170015</v>
+        <v>-84168249.68170023</v>
       </c>
       <c r="C6" t="n">
-        <v>-153741236.2025249</v>
+        <v>-153751757.622525</v>
       </c>
       <c r="D6" t="n">
-        <v>-238136708.8765256</v>
+        <v>-238147230.2965257</v>
       </c>
       <c r="E6" t="n">
-        <v>-307142770.993578</v>
+        <v>-307153292.413578</v>
       </c>
       <c r="F6" t="n">
-        <v>-368238497.9485693</v>
+        <v>-368249019.3685689</v>
       </c>
     </row>
     <row r="7">
@@ -1871,19 +1871,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>968566186.2</v>
+        <v>968556346.2</v>
       </c>
       <c r="C7" t="n">
-        <v>952066232.4</v>
+        <v>952056392.4</v>
       </c>
       <c r="D7" t="n">
-        <v>930332967</v>
+        <v>930323127</v>
       </c>
       <c r="E7" t="n">
-        <v>910165140.2</v>
+        <v>910155300.2</v>
       </c>
       <c r="F7" t="n">
-        <v>892738047.9955593</v>
+        <v>892728207.9955593</v>
       </c>
     </row>
     <row r="8">
@@ -1915,19 +1915,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.751163584157501</v>
+        <v>0.7511640703798452</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7735695811270393</v>
+        <v>0.7735700578156122</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8013774898610432</v>
+        <v>0.8013779572027812</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8185024164011219</v>
+        <v>0.8185028745792965</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8312398560129138</v>
+        <v>0.8312403052072024</v>
       </c>
     </row>
     <row r="10">
@@ -1937,19 +1937,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9122710552904771</v>
+        <v>0.9122716457964342</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9394826280175572</v>
+        <v>0.9394832069449661</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9732546994827147</v>
+        <v>0.9732552670586057</v>
       </c>
       <c r="E10" t="n">
-        <v>0.994052532519325</v>
+        <v>0.9940530889662771</v>
       </c>
       <c r="F10" t="n">
-        <v>1.009521862664477</v>
+        <v>1.009522408200704</v>
       </c>
     </row>
     <row r="11">
@@ -1959,19 +1959,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.006271055290477112</v>
+        <v>0.006271645796434133</v>
       </c>
       <c r="C11" t="n">
-        <v>0.03348262801755719</v>
+        <v>0.03348320694496609</v>
       </c>
       <c r="D11" t="n">
-        <v>0.06725469948271467</v>
+        <v>0.06725526705860563</v>
       </c>
       <c r="E11" t="n">
-        <v>0.08805253251932499</v>
+        <v>0.08805308896627706</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1035218626644773</v>
+        <v>0.1035224082007044</v>
       </c>
     </row>
     <row r="12">
@@ -1981,19 +1981,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06227105529047716</v>
+        <v>0.04727164579643417</v>
       </c>
       <c r="C12" t="n">
-        <v>0.08948262801755724</v>
+        <v>0.07448320694496613</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1232546994827147</v>
+        <v>0.1082552670586057</v>
       </c>
       <c r="E12" t="n">
-        <v>0.144052532519325</v>
+        <v>0.1290530889662771</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1595218626644773</v>
+        <v>0.1445224082007044</v>
       </c>
     </row>
     <row r="13">
@@ -2025,19 +2025,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07173265227202844</v>
+        <v>0.07173347856775743</v>
       </c>
       <c r="C14" t="n">
-        <v>0.07574195647752228</v>
+        <v>0.07574283107201978</v>
       </c>
       <c r="D14" t="n">
-        <v>0.08132324401045617</v>
+        <v>0.0813241914919593</v>
       </c>
       <c r="E14" t="n">
-        <v>0.08418668597986075</v>
+        <v>0.08418767649789095</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08449170050007533</v>
+        <v>0.08449270163217075</v>
       </c>
     </row>
     <row r="15">
@@ -2047,19 +2047,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>60367967.2265</v>
+        <v>60365507.2265</v>
       </c>
       <c r="C15" t="n">
-        <v>51680376.77942753</v>
+        <v>51677916.77942753</v>
       </c>
       <c r="D15" t="n">
-        <v>39435337.84870747</v>
+        <v>39432877.84870747</v>
       </c>
       <c r="E15" t="n">
-        <v>33063143.38766223</v>
+        <v>33060683.38766223</v>
       </c>
       <c r="F15" t="n">
-        <v>32197866.75511277</v>
+        <v>32195406.75511277</v>
       </c>
     </row>
     <row r="16">
@@ -2091,19 +2091,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>50566271.73829985</v>
+        <v>50555750.31829977</v>
       </c>
       <c r="C17" t="n">
-        <v>-103174964.4642251</v>
+        <v>-103196007.3042252</v>
       </c>
       <c r="D17" t="n">
-        <v>-341311673.3407507</v>
+        <v>-341343237.6007509</v>
       </c>
       <c r="E17" t="n">
-        <v>-648454444.3343287</v>
+        <v>-648496530.014329</v>
       </c>
       <c r="F17" t="n">
-        <v>-1016692942.282898</v>
+        <v>-1016745549.382898</v>
       </c>
     </row>
     <row r="18">
@@ -2113,19 +2113,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>160170582.169875</v>
+        <v>160168737.169875</v>
       </c>
       <c r="C18" t="n">
-        <v>159783218.0845706</v>
+        <v>159781373.0845706</v>
       </c>
       <c r="D18" t="n">
-        <v>158359960.3865306</v>
+        <v>158358115.3865306</v>
       </c>
       <c r="E18" t="n">
-        <v>156813160.7907467</v>
+        <v>156811315.7907467</v>
       </c>
       <c r="F18" t="n">
-        <v>155712752.8163345</v>
+        <v>155710907.8163345</v>
       </c>
     </row>
     <row r="19">
@@ -2211,19 +2211,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2198488305.95</v>
+        <v>2198479080.95</v>
       </c>
       <c r="C2" t="n">
-        <v>2249401986.8475</v>
+        <v>2249392761.8475</v>
       </c>
       <c r="D2" t="n">
-        <v>2288420584.139875</v>
+        <v>2288411359.139875</v>
       </c>
       <c r="E2" t="n">
-        <v>2316145694.774869</v>
+        <v>2316136469.774869</v>
       </c>
       <c r="F2" t="n">
-        <v>2348583661.661071</v>
+        <v>2348574436.661071</v>
       </c>
     </row>
     <row r="3">
@@ -2233,19 +2233,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1787407950</v>
+        <v>1787398725</v>
       </c>
       <c r="C3" t="n">
-        <v>1828111264</v>
+        <v>1828102039</v>
       </c>
       <c r="D3" t="n">
-        <v>1856564154</v>
+        <v>1856554929</v>
       </c>
       <c r="E3" t="n">
-        <v>1873353634</v>
+        <v>1873344409</v>
       </c>
       <c r="F3" t="n">
-        <v>1894470799.488898</v>
+        <v>1894461574.488898</v>
       </c>
     </row>
     <row r="4">
@@ -2255,19 +2255,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1022933569.785</v>
+        <v>1022928290.3175</v>
       </c>
       <c r="C4" t="n">
-        <v>1046228076.3872</v>
+        <v>1046222796.9197</v>
       </c>
       <c r="D4" t="n">
-        <v>1062511665.3342</v>
+        <v>1062506385.8667</v>
       </c>
       <c r="E4" t="n">
-        <v>1072120284.7382</v>
+        <v>1072115005.2707</v>
       </c>
       <c r="F4" t="n">
-        <v>1084205638.547497</v>
+        <v>1084200359.079997</v>
       </c>
     </row>
     <row r="5">
@@ -2277,19 +2277,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2253370605.515</v>
+        <v>2253365326.0475</v>
       </c>
       <c r="C5" t="n">
-        <v>2347385816.5172</v>
+        <v>2347380537.0497</v>
       </c>
       <c r="D5" t="n">
-        <v>2443376761.3542</v>
+        <v>2443371481.8867</v>
       </c>
       <c r="E5" t="n">
-        <v>2516683364.4082</v>
+        <v>2516678084.9407</v>
       </c>
       <c r="F5" t="n">
-        <v>2587189145.347497</v>
+        <v>2587183865.879996</v>
       </c>
     </row>
     <row r="6">
@@ -2299,19 +2299,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-54882299.56500006</v>
+        <v>-54886245.09750032</v>
       </c>
       <c r="C6" t="n">
-        <v>-97983829.66970015</v>
+        <v>-97987775.20219994</v>
       </c>
       <c r="D6" t="n">
-        <v>-154956177.214325</v>
+        <v>-154960122.7468252</v>
       </c>
       <c r="E6" t="n">
-        <v>-200537669.6333313</v>
+        <v>-200541615.1658311</v>
       </c>
       <c r="F6" t="n">
-        <v>-238605483.6864257</v>
+        <v>-238609429.2189255</v>
       </c>
     </row>
     <row r="7">
@@ -2321,19 +2321,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1008903590.2</v>
+        <v>1008899900.2</v>
       </c>
       <c r="C7" t="n">
-        <v>1027152075.4</v>
+        <v>1027148385.4</v>
       </c>
       <c r="D7" t="n">
-        <v>1038124169</v>
+        <v>1038120479</v>
       </c>
       <c r="E7" t="n">
-        <v>1044391386.2</v>
+        <v>1044387696.2</v>
       </c>
       <c r="F7" t="n">
-        <v>1052349936.995559</v>
+        <v>1052346246.995559</v>
       </c>
     </row>
     <row r="8">
@@ -2365,19 +2365,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7516872938691953</v>
+        <v>0.7516874744323476</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7718816971326583</v>
+        <v>0.7718818724366894</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7827259599118203</v>
+        <v>0.7827261275551162</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7891222697277621</v>
+        <v>0.7891224317019607</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7906250897948539</v>
+        <v>0.7906252462916642</v>
       </c>
     </row>
     <row r="10">
@@ -2387,19 +2387,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9129070888009263</v>
+        <v>0.91290730809076</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9374327313702259</v>
+        <v>0.9374329442729767</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9506028413942483</v>
+        <v>0.9506030449932109</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9583710139052983</v>
+        <v>0.9583712106192714</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9601961546302115</v>
+        <v>0.9601963446920212</v>
       </c>
     </row>
     <row r="11">
@@ -2409,19 +2409,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.006907088800926275</v>
+        <v>0.006907308090760012</v>
       </c>
       <c r="C11" t="n">
-        <v>0.03143273137022584</v>
+        <v>0.03143294427297672</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0446028413942483</v>
+        <v>0.04460304499321088</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0523710139052983</v>
+        <v>0.05237121061927141</v>
       </c>
       <c r="F11" t="n">
-        <v>0.05419615463021143</v>
+        <v>0.05419634469202117</v>
       </c>
     </row>
     <row r="12">
@@ -2431,19 +2431,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06290708880092633</v>
+        <v>0.04790730809076005</v>
       </c>
       <c r="C12" t="n">
-        <v>0.08743273137022589</v>
+        <v>0.07243294427297675</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1006028413942484</v>
+        <v>0.08560304499321092</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1083710139052984</v>
+        <v>0.09337121061927145</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1101961546302115</v>
+        <v>0.09519634469202121</v>
       </c>
     </row>
     <row r="13">
@@ -2475,19 +2475,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06968097514341932</v>
+        <v>0.06968126753055244</v>
       </c>
       <c r="C14" t="n">
-        <v>0.07173636146118502</v>
+        <v>0.07173665565966636</v>
       </c>
       <c r="D14" t="n">
-        <v>0.07503484158028553</v>
+        <v>0.07503514405930042</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07599740871098758</v>
+        <v>0.07599771140303725</v>
       </c>
       <c r="F14" t="n">
-        <v>0.07469145760638231</v>
+        <v>0.07469175098805489</v>
       </c>
     </row>
     <row r="15">
@@ -2497,19 +2497,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>66656021.595</v>
+        <v>66655099.095</v>
       </c>
       <c r="C15" t="n">
-        <v>63576284.68474999</v>
+        <v>63575362.18474999</v>
       </c>
       <c r="D15" t="n">
-        <v>57130782.41398752</v>
+        <v>57129859.91398752</v>
       </c>
       <c r="E15" t="n">
-        <v>55593498.47748691</v>
+        <v>55592575.97748691</v>
       </c>
       <c r="F15" t="n">
-        <v>59439229.16610709</v>
+        <v>59438306.66610709</v>
       </c>
     </row>
     <row r="16">
@@ -2541,19 +2541,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>79841700.43499994</v>
+        <v>79837754.90249968</v>
       </c>
       <c r="C17" t="n">
-        <v>-18142129.2347002</v>
+        <v>-18150020.29970026</v>
       </c>
       <c r="D17" t="n">
-        <v>-173098306.4490252</v>
+        <v>-173110143.0465255</v>
       </c>
       <c r="E17" t="n">
-        <v>-373635976.0823565</v>
+        <v>-373651758.2123566</v>
       </c>
       <c r="F17" t="n">
-        <v>-612241459.7687821</v>
+        <v>-612261187.431282</v>
       </c>
     </row>
     <row r="18">
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>164886622.94625</v>
+        <v>164885931.07125</v>
       </c>
       <c r="C18" t="n">
-        <v>168705149.0135625</v>
+        <v>168704457.1385625</v>
       </c>
       <c r="D18" t="n">
-        <v>171631543.8104906</v>
+        <v>171630851.9354906</v>
       </c>
       <c r="E18" t="n">
-        <v>173710927.1081152</v>
+        <v>173710235.2331152</v>
       </c>
       <c r="F18" t="n">
-        <v>176143774.6245803</v>
+        <v>176143082.7495803</v>
       </c>
     </row>
     <row r="19">
@@ -2797,19 +2797,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>485962428</v>
+        <v>485937828</v>
       </c>
       <c r="D7" t="n">
-        <v>529624166</v>
+        <v>529599566</v>
       </c>
       <c r="E7" t="n">
-        <v>548683640</v>
+        <v>548659040</v>
       </c>
       <c r="F7" t="n">
-        <v>561413618</v>
+        <v>561389018</v>
       </c>
       <c r="G7" t="n">
-        <v>578540607.4888983</v>
+        <v>578516007.4888983</v>
       </c>
     </row>
     <row r="8">
@@ -3337,19 +3337,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>486833678</v>
+        <v>486824453</v>
       </c>
       <c r="D27" t="n">
-        <v>530495416</v>
+        <v>530486191</v>
       </c>
       <c r="E27" t="n">
-        <v>555970390</v>
+        <v>555961165</v>
       </c>
       <c r="F27" t="n">
-        <v>569687368</v>
+        <v>569678143</v>
       </c>
       <c r="G27" t="n">
-        <v>587636857.4888983</v>
+        <v>587627632.4888983</v>
       </c>
     </row>
     <row r="28">
@@ -4791,19 +4791,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>989297254.7967</v>
+        <v>989283176.2167001</v>
       </c>
       <c r="E16" t="n">
-        <v>982964003.8668001</v>
+        <v>982949925.2868</v>
       </c>
       <c r="F16" t="n">
-        <v>968644151.3436</v>
+        <v>968630072.7636001</v>
       </c>
       <c r="G16" t="n">
-        <v>953297035.2002001</v>
+        <v>953282956.6202</v>
       </c>
       <c r="H16" t="n">
-        <v>941269028.6996965</v>
+        <v>941254950.1196965</v>
       </c>
     </row>
     <row r="17">
@@ -5271,19 +5271,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1022933569.785</v>
+        <v>1022928290.3175</v>
       </c>
       <c r="E31" t="n">
-        <v>1046228076.3872</v>
+        <v>1046222796.9197</v>
       </c>
       <c r="F31" t="n">
-        <v>1062511665.3342</v>
+        <v>1062506385.8667</v>
       </c>
       <c r="G31" t="n">
-        <v>1072120284.7382</v>
+        <v>1072115005.2707</v>
       </c>
       <c r="H31" t="n">
-        <v>1084205638.547497</v>
+        <v>1084200359.079997</v>
       </c>
     </row>
     <row r="32">
@@ -5839,19 +5839,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60367967.2265</v>
+        <v>60365507.2265</v>
       </c>
       <c r="C3" t="n">
-        <v>51471276.77942753</v>
+        <v>51465126.77942753</v>
       </c>
       <c r="D3" t="n">
-        <v>39226237.84870747</v>
+        <v>39220087.84870747</v>
       </c>
       <c r="E3" t="n">
-        <v>32854043.38766223</v>
+        <v>32847893.38766223</v>
       </c>
       <c r="F3" t="n">
-        <v>31988766.75511277</v>
+        <v>31982616.75511277</v>
       </c>
     </row>
     <row r="4">
@@ -5861,19 +5861,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07173265227202844</v>
+        <v>0.07173347856775743</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07581636918644251</v>
+        <v>0.07581856000903321</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08140385883335952</v>
+        <v>0.08140623227713141</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0842709633055249</v>
+        <v>0.08427344460486896</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08457688150935559</v>
+        <v>0.08457938943328519</v>
       </c>
     </row>
     <row r="5">
@@ -5905,19 +5905,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>989297254.7967</v>
+        <v>989283176.2167001</v>
       </c>
       <c r="C6" t="n">
-        <v>981767324.5668</v>
+        <v>981732128.1168001</v>
       </c>
       <c r="D6" t="n">
-        <v>967447472.0436001</v>
+        <v>967412275.5936</v>
       </c>
       <c r="E6" t="n">
-        <v>952100355.9002</v>
+        <v>952065159.4502001</v>
       </c>
       <c r="F6" t="n">
-        <v>940072349.3996966</v>
+        <v>940037152.9496965</v>
       </c>
     </row>
     <row r="7">
@@ -5927,19 +5927,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1728634029</v>
+        <v>1728609429</v>
       </c>
       <c r="C7" t="n">
-        <v>1715476716</v>
+        <v>1715415216</v>
       </c>
       <c r="D7" t="n">
-        <v>1690455132</v>
+        <v>1690393632</v>
       </c>
       <c r="E7" t="n">
-        <v>1663638574</v>
+        <v>1663577074</v>
       </c>
       <c r="F7" t="n">
-        <v>1642621613.488898</v>
+        <v>1642560113.488898</v>
       </c>
     </row>
     <row r="8">
@@ -5949,19 +5949,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-84157728.26170015</v>
+        <v>-84168249.68170023</v>
       </c>
       <c r="C8" t="n">
-        <v>-154635556.9025247</v>
+        <v>-154661860.4525254</v>
       </c>
       <c r="D8" t="n">
-        <v>-239031029.5765259</v>
+        <v>-239057333.1265256</v>
       </c>
       <c r="E8" t="n">
-        <v>-308037091.6935778</v>
+        <v>-308063395.243578</v>
       </c>
       <c r="F8" t="n">
-        <v>-369132818.6485691</v>
+        <v>-369159122.1985688</v>
       </c>
     </row>
     <row r="9">
@@ -5971,19 +5971,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2219765490.5267</v>
+        <v>2219751411.9467</v>
       </c>
       <c r="C9" t="n">
-        <v>2282987464.6968</v>
+        <v>2282952268.2468</v>
       </c>
       <c r="D9" t="n">
-        <v>2348406168.063601</v>
+        <v>2348370971.6136</v>
       </c>
       <c r="E9" t="n">
-        <v>2396788235.5702</v>
+        <v>2396753039.1202</v>
       </c>
       <c r="F9" t="n">
-        <v>2443211856.199697</v>
+        <v>2443176659.749696</v>
       </c>
     </row>
     <row r="10">
@@ -5993,19 +5993,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2135607762.265</v>
+        <v>2135583162.265</v>
       </c>
       <c r="C10" t="n">
-        <v>2128351907.794275</v>
+        <v>2128290407.794275</v>
       </c>
       <c r="D10" t="n">
-        <v>2109375138.487075</v>
+        <v>2109313638.487075</v>
       </c>
       <c r="E10" t="n">
-        <v>2088751143.876622</v>
+        <v>2088689643.876622</v>
       </c>
       <c r="F10" t="n">
-        <v>2074079037.551127</v>
+        <v>2074017537.551127</v>
       </c>
     </row>
     <row r="11">
@@ -6015,19 +6015,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50566271.73829985</v>
+        <v>50555750.31829977</v>
       </c>
       <c r="C11" t="n">
-        <v>-104069285.1642249</v>
+        <v>-104106110.1342256</v>
       </c>
       <c r="D11" t="n">
-        <v>-343100314.7407508</v>
+        <v>-343163443.2607512</v>
       </c>
       <c r="E11" t="n">
-        <v>-651137406.4343286</v>
+        <v>-651226838.5043292</v>
       </c>
       <c r="F11" t="n">
-        <v>-1020270225.082898</v>
+        <v>-1020385960.702898</v>
       </c>
     </row>
     <row r="12">
@@ -6059,19 +6059,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>160170582.169875</v>
+        <v>160168737.169875</v>
       </c>
       <c r="C13" t="n">
-        <v>159626393.0845706</v>
+        <v>159621780.5845706</v>
       </c>
       <c r="D13" t="n">
-        <v>158203135.3865306</v>
+        <v>158198522.8865306</v>
       </c>
       <c r="E13" t="n">
-        <v>156656335.7907467</v>
+        <v>156651723.2907467</v>
       </c>
       <c r="F13" t="n">
-        <v>155555927.8163345</v>
+        <v>155551315.3163345</v>
       </c>
     </row>
   </sheetData>
